--- a/artfynd/A 63921-2023 artfynd.xlsx
+++ b/artfynd/A 63921-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -908,6 +908,114 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114669986</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57248</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen (Abborrtjärnen), Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>321116</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6580946</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-02-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-02-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63921-2023 artfynd.xlsx
+++ b/artfynd/A 63921-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63921-2023 artfynd.xlsx
+++ b/artfynd/A 63921-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1016,6 +1016,635 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128719053</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96837</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>53</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nordost om Abborrtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>321413</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6581011</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Låga # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128719405</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96837</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>53</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nordost om Abborrtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>321424</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6581013</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Låga # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128719750</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96837</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>53</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nordost om Abborrtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>321440</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6581011</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128718958</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92163</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norr om Abborrtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>321311</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6580942</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Blåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Torrgran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128719239</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96837</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>53</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nordost om Abborrtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>321412</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6581000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63921-2023 artfynd.xlsx
+++ b/artfynd/A 63921-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,7 +1021,7 @@
         <v>128719053</v>
       </c>
       <c r="B5" t="n">
-        <v>96837</v>
+        <v>96838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>128719405</v>
       </c>
       <c r="B6" t="n">
-        <v>96837</v>
+        <v>96838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128719750</v>
       </c>
       <c r="B7" t="n">
-        <v>96837</v>
+        <v>96838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128718958</v>
       </c>
       <c r="B8" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128719239</v>
       </c>
       <c r="B9" t="n">
-        <v>96837</v>
+        <v>96838</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1644,6 +1644,1148 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128814096</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skansen S/O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>321329</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6581025</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128814061</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skansen S/O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>321347</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6581029</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128814115</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skansen S, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>321317</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6581007</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128812736</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skansen S/O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>321174</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6581001</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128814347</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skansen S, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>321087</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6580989</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128812529</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91487</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skansen S/O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>321292</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6581028</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128814456</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skansen S, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>321322</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6580953</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128814045</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skansen S/O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>321366</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6581001</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128814374</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skansen S, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>321140</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6580938</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128814476</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98592</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skansen S, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>321361</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6580962</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63921-2023 artfynd.xlsx
+++ b/artfynd/A 63921-2023 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>128719053</v>
       </c>
       <c r="B5" t="n">
-        <v>96838</v>
+        <v>96865</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>128719405</v>
       </c>
       <c r="B6" t="n">
-        <v>96838</v>
+        <v>96865</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128719750</v>
       </c>
       <c r="B7" t="n">
-        <v>96838</v>
+        <v>96865</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128718958</v>
       </c>
       <c r="B8" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128719239</v>
       </c>
       <c r="B9" t="n">
-        <v>96838</v>
+        <v>96865</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>128814096</v>
       </c>
       <c r="B10" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>128814061</v>
       </c>
       <c r="B11" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128814115</v>
       </c>
       <c r="B12" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>128812736</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>128814347</v>
       </c>
       <c r="B14" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>128812529</v>
       </c>
       <c r="B15" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>128814456</v>
       </c>
       <c r="B16" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>128814045</v>
       </c>
       <c r="B17" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>128814374</v>
       </c>
       <c r="B18" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128814476</v>
       </c>
       <c r="B19" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 63921-2023 artfynd.xlsx
+++ b/artfynd/A 63921-2023 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>128719053</v>
       </c>
       <c r="B5" t="n">
-        <v>96865</v>
+        <v>96871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>128719405</v>
       </c>
       <c r="B6" t="n">
-        <v>96865</v>
+        <v>96871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128719750</v>
       </c>
       <c r="B7" t="n">
-        <v>96865</v>
+        <v>96871</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128718958</v>
       </c>
       <c r="B8" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128719239</v>
       </c>
       <c r="B9" t="n">
-        <v>96865</v>
+        <v>96871</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>128814096</v>
       </c>
       <c r="B10" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>128814061</v>
       </c>
       <c r="B11" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128814115</v>
       </c>
       <c r="B12" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>128812736</v>
       </c>
       <c r="B13" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>128814347</v>
       </c>
       <c r="B14" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>128812529</v>
       </c>
       <c r="B15" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>128814456</v>
       </c>
       <c r="B16" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>128814045</v>
       </c>
       <c r="B17" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>128814374</v>
       </c>
       <c r="B18" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128814476</v>
       </c>
       <c r="B19" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 63921-2023 artfynd.xlsx
+++ b/artfynd/A 63921-2023 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>128719053</v>
       </c>
       <c r="B5" t="n">
-        <v>96871</v>
+        <v>96878</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>128719405</v>
       </c>
       <c r="B6" t="n">
-        <v>96871</v>
+        <v>96878</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128719750</v>
       </c>
       <c r="B7" t="n">
-        <v>96871</v>
+        <v>96878</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128718958</v>
       </c>
       <c r="B8" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128719239</v>
       </c>
       <c r="B9" t="n">
-        <v>96871</v>
+        <v>96878</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>128814096</v>
       </c>
       <c r="B10" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>128814061</v>
       </c>
       <c r="B11" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128814115</v>
       </c>
       <c r="B12" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>128814347</v>
       </c>
       <c r="B14" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>128812529</v>
       </c>
       <c r="B15" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>128814456</v>
       </c>
       <c r="B16" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>128814045</v>
       </c>
       <c r="B17" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>128814374</v>
       </c>
       <c r="B18" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128814476</v>
       </c>
       <c r="B19" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 63921-2023 artfynd.xlsx
+++ b/artfynd/A 63921-2023 artfynd.xlsx
@@ -1980,52 +1980,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128812736</v>
+        <v>128814347</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen S, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>321174</v>
+        <v>321087</v>
       </c>
       <c r="R13" t="n">
-        <v>6581001</v>
+        <v>6580989</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2072,22 +2073,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Mosseblåbärbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Mossebärljungbarrskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2105,53 +2091,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128814347</v>
+        <v>128812736</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skansen S, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>321087</v>
+        <v>321174</v>
       </c>
       <c r="R14" t="n">
-        <v>6580989</v>
+        <v>6581001</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2198,7 +2183,22 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 63921-2023 artfynd.xlsx
+++ b/artfynd/A 63921-2023 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>128719053</v>
       </c>
       <c r="B5" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>128719405</v>
       </c>
       <c r="B6" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128719750</v>
       </c>
       <c r="B7" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128718958</v>
       </c>
       <c r="B8" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128719239</v>
       </c>
       <c r="B9" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>128814096</v>
       </c>
       <c r="B10" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>128814061</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128814115</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,53 +1980,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128814347</v>
+        <v>128812736</v>
       </c>
       <c r="B13" t="n">
-        <v>98632</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skansen S, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>321087</v>
+        <v>321174</v>
       </c>
       <c r="R13" t="n">
-        <v>6580989</v>
+        <v>6581001</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2073,7 +2072,22 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2091,52 +2105,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128812736</v>
+        <v>128814347</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen S, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>321174</v>
+        <v>321087</v>
       </c>
       <c r="R14" t="n">
-        <v>6581001</v>
+        <v>6580989</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2183,22 +2198,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Mosseblåbärbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Mossebärljungbarrskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
         <v>128812529</v>
       </c>
       <c r="B15" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>128814456</v>
       </c>
       <c r="B16" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>128814045</v>
       </c>
       <c r="B17" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>128814374</v>
       </c>
       <c r="B18" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128814476</v>
       </c>
       <c r="B19" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 63921-2023 artfynd.xlsx
+++ b/artfynd/A 63921-2023 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>128719053</v>
       </c>
       <c r="B5" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>128719405</v>
       </c>
       <c r="B6" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128719750</v>
       </c>
       <c r="B7" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128718958</v>
       </c>
       <c r="B8" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128719239</v>
       </c>
       <c r="B9" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>128814096</v>
       </c>
       <c r="B10" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>128814061</v>
       </c>
       <c r="B11" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128814115</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,52 +1980,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128812736</v>
+        <v>128814347</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>98643</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen S, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>321174</v>
+        <v>321087</v>
       </c>
       <c r="R13" t="n">
-        <v>6581001</v>
+        <v>6580989</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2072,22 +2073,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Mosseblåbärbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Mossebärljungbarrskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2105,53 +2091,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128814347</v>
+        <v>128812736</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skansen S, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>321087</v>
+        <v>321174</v>
       </c>
       <c r="R14" t="n">
-        <v>6580989</v>
+        <v>6581001</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2198,7 +2183,22 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
         <v>128812529</v>
       </c>
       <c r="B15" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>128814456</v>
       </c>
       <c r="B16" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>128814045</v>
       </c>
       <c r="B17" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>128814374</v>
       </c>
       <c r="B18" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128814476</v>
       </c>
       <c r="B19" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 63921-2023 artfynd.xlsx
+++ b/artfynd/A 63921-2023 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>128719053</v>
       </c>
       <c r="B5" t="n">
-        <v>96897</v>
+        <v>96902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>128719405</v>
       </c>
       <c r="B6" t="n">
-        <v>96897</v>
+        <v>96902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128719750</v>
       </c>
       <c r="B7" t="n">
-        <v>96897</v>
+        <v>96902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128718958</v>
       </c>
       <c r="B8" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128719239</v>
       </c>
       <c r="B9" t="n">
-        <v>96897</v>
+        <v>96902</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>128814096</v>
       </c>
       <c r="B10" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>128814061</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128814115</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>128814347</v>
       </c>
       <c r="B14" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>128812529</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>128814456</v>
       </c>
       <c r="B16" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>128814045</v>
       </c>
       <c r="B17" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>128814374</v>
       </c>
       <c r="B18" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128814476</v>
       </c>
       <c r="B19" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 63921-2023 artfynd.xlsx
+++ b/artfynd/A 63921-2023 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>128719053</v>
       </c>
       <c r="B5" t="n">
-        <v>96902</v>
+        <v>96905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>128719405</v>
       </c>
       <c r="B6" t="n">
-        <v>96902</v>
+        <v>96905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128719750</v>
       </c>
       <c r="B7" t="n">
-        <v>96902</v>
+        <v>96905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128718958</v>
       </c>
       <c r="B8" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128719239</v>
       </c>
       <c r="B9" t="n">
-        <v>96902</v>
+        <v>96905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>128814096</v>
       </c>
       <c r="B10" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>128814061</v>
       </c>
       <c r="B11" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128814115</v>
       </c>
       <c r="B12" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>128812736</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>128814347</v>
       </c>
       <c r="B14" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>128812529</v>
       </c>
       <c r="B15" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>128814456</v>
       </c>
       <c r="B16" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>128814045</v>
       </c>
       <c r="B17" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>128814374</v>
       </c>
       <c r="B18" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128814476</v>
       </c>
       <c r="B19" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 63921-2023 artfynd.xlsx
+++ b/artfynd/A 63921-2023 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>128719053</v>
       </c>
       <c r="B5" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>128719405</v>
       </c>
       <c r="B6" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128719750</v>
       </c>
       <c r="B7" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128718958</v>
       </c>
       <c r="B8" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128719239</v>
       </c>
       <c r="B9" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>128814096</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>128814061</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128814115</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,52 +1980,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128812736</v>
+        <v>128814347</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen S, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>321174</v>
+        <v>321087</v>
       </c>
       <c r="R13" t="n">
-        <v>6581001</v>
+        <v>6580989</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2072,22 +2073,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Mosseblåbärbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Mossebärljungbarrskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2105,53 +2091,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128814347</v>
+        <v>128812736</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skansen S, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>321087</v>
+        <v>321174</v>
       </c>
       <c r="R14" t="n">
-        <v>6580989</v>
+        <v>6581001</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2198,7 +2183,22 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
         <v>128812529</v>
       </c>
       <c r="B15" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>128814456</v>
       </c>
       <c r="B16" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>128814045</v>
       </c>
       <c r="B17" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>128814374</v>
       </c>
       <c r="B18" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128814476</v>
       </c>
       <c r="B19" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 63921-2023 artfynd.xlsx
+++ b/artfynd/A 63921-2023 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>128814096</v>
       </c>
       <c r="B10" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>128814061</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128814115</v>
       </c>
       <c r="B12" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,53 +1980,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128814347</v>
+        <v>128812736</v>
       </c>
       <c r="B13" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skansen S, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>321087</v>
+        <v>321174</v>
       </c>
       <c r="R13" t="n">
-        <v>6580989</v>
+        <v>6581001</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2073,7 +2072,22 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2091,52 +2105,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128812736</v>
+        <v>128814347</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen S, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>321174</v>
+        <v>321087</v>
       </c>
       <c r="R14" t="n">
-        <v>6581001</v>
+        <v>6580989</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2183,22 +2198,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Mosseblåbärbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Mossebärljungbarrskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
         <v>128812529</v>
       </c>
       <c r="B15" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>128814456</v>
       </c>
       <c r="B16" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>128814045</v>
       </c>
       <c r="B17" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>128814374</v>
       </c>
       <c r="B18" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128814476</v>
       </c>
       <c r="B19" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 63921-2023 artfynd.xlsx
+++ b/artfynd/A 63921-2023 artfynd.xlsx
@@ -1021,7 +1021,7 @@
         <v>128719053</v>
       </c>
       <c r="B5" t="n">
-        <v>96915</v>
+        <v>96924</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>128719405</v>
       </c>
       <c r="B6" t="n">
-        <v>96915</v>
+        <v>96924</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128719750</v>
       </c>
       <c r="B7" t="n">
-        <v>96915</v>
+        <v>96924</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>128718958</v>
       </c>
       <c r="B8" t="n">
-        <v>92233</v>
+        <v>92242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128719239</v>
       </c>
       <c r="B9" t="n">
-        <v>96915</v>
+        <v>96924</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>128814096</v>
       </c>
       <c r="B10" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>128814061</v>
       </c>
       <c r="B11" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128814115</v>
       </c>
       <c r="B12" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,52 +1980,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128812736</v>
+        <v>128814347</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen S, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>321174</v>
+        <v>321087</v>
       </c>
       <c r="R13" t="n">
-        <v>6581001</v>
+        <v>6580989</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2072,22 +2073,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Mosseblåbärbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Mossebärljungbarrskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2105,53 +2091,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128814347</v>
+        <v>128812736</v>
       </c>
       <c r="B14" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skansen S, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>321087</v>
+        <v>321174</v>
       </c>
       <c r="R14" t="n">
-        <v>6580989</v>
+        <v>6581001</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2198,7 +2183,22 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
         <v>128812529</v>
       </c>
       <c r="B15" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>128814456</v>
       </c>
       <c r="B16" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>128814045</v>
       </c>
       <c r="B17" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>128814374</v>
       </c>
       <c r="B18" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128814476</v>
       </c>
       <c r="B19" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 63921-2023 artfynd.xlsx
+++ b/artfynd/A 63921-2023 artfynd.xlsx
@@ -1980,53 +1980,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128814347</v>
+        <v>128812736</v>
       </c>
       <c r="B13" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skansen S, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>321087</v>
+        <v>321174</v>
       </c>
       <c r="R13" t="n">
-        <v>6580989</v>
+        <v>6581001</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2073,7 +2072,22 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2091,52 +2105,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128812736</v>
+        <v>128814347</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Skansen S, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>321174</v>
+        <v>321087</v>
       </c>
       <c r="R14" t="n">
-        <v>6581001</v>
+        <v>6580989</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2183,22 +2198,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Mosseblåbärbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Mossebärljungbarrskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 63921-2023 artfynd.xlsx
+++ b/artfynd/A 63921-2023 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>128814096</v>
       </c>
       <c r="B10" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>128814061</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128814115</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>128814347</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>128812529</v>
       </c>
       <c r="B15" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>128814456</v>
       </c>
       <c r="B16" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>128814045</v>
       </c>
       <c r="B17" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>128814374</v>
       </c>
       <c r="B18" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128814476</v>
       </c>
       <c r="B19" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 63921-2023 artfynd.xlsx
+++ b/artfynd/A 63921-2023 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>128814096</v>
       </c>
       <c r="B10" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>128814061</v>
       </c>
       <c r="B11" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>128814115</v>
       </c>
       <c r="B12" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>128814347</v>
       </c>
       <c r="B14" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>128812529</v>
       </c>
       <c r="B15" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>128814456</v>
       </c>
       <c r="B16" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>128814045</v>
       </c>
       <c r="B17" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>128814374</v>
       </c>
       <c r="B18" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>128814476</v>
       </c>
       <c r="B19" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 63921-2023 artfynd.xlsx
+++ b/artfynd/A 63921-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114512144</v>
+        <v>128719053</v>
       </c>
       <c r="B2" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Abborrtjärnen (Abborrtjärnen), Vrm</t>
+          <t>Nordost om Abborrtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>321122</v>
+        <v>321413</v>
       </c>
       <c r="R2" t="n">
-        <v>6580897</v>
+        <v>6581011</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:09</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:09</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,69 +762,92 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Låga # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114511676</v>
+        <v>128719239</v>
       </c>
       <c r="B3" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Vrm</t>
+          <t>Nordost om Abborrtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>321164</v>
+        <v>321412</v>
       </c>
       <c r="R3" t="n">
-        <v>6580932</v>
+        <v>6581000</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,27 +874,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,33 +888,49 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114669986</v>
+        <v>128719405</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,43 +938,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Abborrtjärnen (Abborrtjärnen), Vrm</t>
+          <t>Nordost om Abborrtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>321117</v>
+        <v>321424</v>
       </c>
       <c r="R4" t="n">
-        <v>6580946</v>
+        <v>6581013</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,12 +1000,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,28 +1014,49 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Låga # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128719053</v>
+        <v>128719625</v>
       </c>
       <c r="B5" t="n">
-        <v>96924</v>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1061,10 +1096,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>321413</v>
+        <v>321439</v>
       </c>
       <c r="R5" t="n">
-        <v>6581011</v>
+        <v>6581034</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,17 +1151,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Låga # Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1144,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128719405</v>
+        <v>128719750</v>
       </c>
       <c r="B6" t="n">
-        <v>96924</v>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,10 +1222,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321424</v>
+        <v>321440</v>
       </c>
       <c r="R6" t="n">
-        <v>6581013</v>
+        <v>6581011</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,17 +1277,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Låga # Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1270,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128719750</v>
+        <v>131939251</v>
       </c>
       <c r="B7" t="n">
-        <v>96924</v>
+        <v>97435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,24 +1334,20 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nordost om Abborrtjärnen, Vrm</t>
+          <t>Nordväst Abborrtjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>321440</v>
+        <v>321205</v>
       </c>
       <c r="R7" t="n">
-        <v>6581011</v>
+        <v>6580984</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,12 +1374,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,94 +1388,66 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Roger Gran, Lina Lejonberg, Jan Rees, Emma Enfjäll</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128718958</v>
+        <v>251453</v>
       </c>
       <c r="B8" t="n">
-        <v>92242</v>
+        <v>83299</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norr om Abborrtjärnen, Vrm</t>
+          <t>NORR ABBORRTJÄRN (10B7f01), Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>321311</v>
+        <v>321393</v>
       </c>
       <c r="R8" t="n">
-        <v>6580942</v>
+        <v>6581004</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1468,12 +1471,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>1994-10-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>1994-10-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>100175011 / CHA GRAC / Enstaka-sparsam (1)  / OBJ.AREA:1,6 ha</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,49 +1490,42 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Lövrik barrnaturskog /</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Torrgran # Picea abies</t>
+          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128719239</v>
+        <v>284227</v>
       </c>
       <c r="B9" t="n">
-        <v>96924</v>
+        <v>81312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,45 +1533,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nordost om Abborrtjärnen, Vrm</t>
+          <t>NORR ABBORRTJÄRN (10B7f01), Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>321412</v>
+        <v>321393</v>
       </c>
       <c r="R9" t="n">
-        <v>6581000</v>
+        <v>6581004</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1594,12 +1587,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>1994-10-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>1994-10-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>100175011 / MIC AHLN / Enstaka-sparsam (1)  / OBJ.AREA:1,6 ha</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,95 +1606,87 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Lövrik barrnaturskog /</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128814096</v>
+        <v>128718958</v>
       </c>
       <c r="B10" t="n">
-        <v>98705</v>
+        <v>92632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Norr om Abborrtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>321329</v>
+        <v>321311</v>
       </c>
       <c r="R10" t="n">
-        <v>6581025</v>
+        <v>6580942</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1720,12 +1710,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,60 +1730,78 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Blåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Torrgran # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128814061</v>
+        <v>128812529</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1801,10 +1809,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>321347</v>
+        <v>321292</v>
       </c>
       <c r="R11" t="n">
-        <v>6581029</v>
+        <v>6581028</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1851,7 +1859,22 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1869,56 +1892,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128814115</v>
+        <v>114511676</v>
       </c>
       <c r="B12" t="n">
-        <v>98705</v>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skansen S, Vrm</t>
+          <t>Abborrtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>321317</v>
+        <v>321164</v>
       </c>
       <c r="R12" t="n">
-        <v>6581007</v>
+        <v>6580932</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1942,12 +1958,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2024-02-03</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2024-02-03</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1956,79 +1987,69 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Mossebärljungbarrskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128812736</v>
+        <v>131939281</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>91937</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Norr Abborrtjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>321174</v>
+        <v>321456</v>
       </c>
       <c r="R13" t="n">
-        <v>6581001</v>
+        <v>6580974</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2052,12 +2073,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,49 +2087,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Mosseblåbärbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Roger Gran, Lina Lejonberg, Jan Rees, Emma Enfjäll</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128814347</v>
+        <v>128812736</v>
       </c>
       <c r="B14" t="n">
-        <v>98705</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,42 +2116,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skansen S, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>321087</v>
+        <v>321174</v>
       </c>
       <c r="R14" t="n">
-        <v>6580989</v>
+        <v>6581001</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2198,7 +2197,22 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Mossebärljungbarrskog</t>
+          <t>Mosseblåbärbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2216,10 +2230,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128812529</v>
+        <v>1882208</v>
       </c>
       <c r="B15" t="n">
-        <v>91561</v>
+        <v>75428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,48 +2241,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>NORR ABBORRTJÄRN (10B7f01), Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>321292</v>
+        <v>321393</v>
       </c>
       <c r="R15" t="n">
-        <v>6581028</v>
+        <v>6581004</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2292,12 +2295,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>1994-10-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>1994-10-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>100175011 / ART LEUC / Tämligen allmän (2)  / OBJ.AREA:1,6 ha</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,95 +2314,83 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Mosseblåbärbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Lövrik barrnaturskog /</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128814456</v>
+        <v>131939219</v>
       </c>
       <c r="B16" t="n">
-        <v>98705</v>
+        <v>80382</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skansen S, Vrm</t>
+          <t>Skansen, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>321322</v>
+        <v>320961</v>
       </c>
       <c r="R16" t="n">
-        <v>6580953</v>
+        <v>6580946</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2418,12 +2414,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2432,80 +2433,72 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Mossebärljungbarrskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Roger Gran, Lina Lejonberg, Jan Rees, Emma Enfjäll</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128814045</v>
+        <v>114669986</v>
       </c>
       <c r="B17" t="n">
-        <v>98705</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skansen S/O, Vrm</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>321366</v>
+        <v>321117</v>
       </c>
       <c r="R17" t="n">
-        <v>6581001</v>
+        <v>6580946</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2529,12 +2522,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2543,80 +2536,71 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Mossebärljungbarrskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128814374</v>
+        <v>114512144</v>
       </c>
       <c r="B18" t="n">
-        <v>98705</v>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skansen S, Vrm</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>321140</v>
+        <v>321122</v>
       </c>
       <c r="R18" t="n">
-        <v>6580938</v>
+        <v>6580897</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2640,12 +2624,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2024-02-03</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2024-02-03</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2654,34 +2648,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Mossebärljungbarrskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128814476</v>
+        <v>128813980</v>
       </c>
       <c r="B19" t="n">
-        <v>98705</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2717,14 +2705,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skansen S, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>321361</v>
+        <v>321459</v>
       </c>
       <c r="R19" t="n">
-        <v>6580962</v>
+        <v>6581008</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2789,51 +2777,56 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131939281</v>
+        <v>128814045</v>
       </c>
       <c r="B20" t="n">
-        <v>91871</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norr Abborrtjärnet, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>321456</v>
+        <v>321366</v>
       </c>
       <c r="R20" t="n">
-        <v>6580974</v>
+        <v>6581001</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2857,12 +2850,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2871,70 +2864,80 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Tommy Solberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Roger Gran, Lina Lejonberg, Jan Rees, Emma Enfjäll</t>
+          <t>Tommy Solberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131939251</v>
+        <v>128814061</v>
       </c>
       <c r="B21" t="n">
-        <v>97356</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nordväst Abborrtjärnet, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>321205</v>
+        <v>321347</v>
       </c>
       <c r="R21" t="n">
-        <v>6580984</v>
+        <v>6581029</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2958,12 +2961,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2972,69 +2975,80 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Tommy Solberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Roger Gran, Lina Lejonberg, Jan Rees, Emma Enfjäll</t>
+          <t>Tommy Solberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131939219</v>
+        <v>128814096</v>
       </c>
       <c r="B22" t="n">
-        <v>80336</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skansen, Vrm</t>
+          <t>Skansen S/O, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>320961</v>
+        <v>321329</v>
       </c>
       <c r="R22" t="n">
-        <v>6580946</v>
+        <v>6581025</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3058,17 +3072,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3077,21 +3086,693 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Tommy Solberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Roger Gran, Lina Lejonberg, Jan Rees, Emma Enfjäll</t>
+          <t>Tommy Solberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128814115</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skansen S, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>321317</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6581007</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128814238</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skansen S, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>321161</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6581017</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128814347</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skansen S, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>321087</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6580989</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128814374</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skansen S, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>321140</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6580938</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128814456</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skansen S, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>321322</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6580953</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128814476</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skansen S, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>321361</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6580962</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Trankil</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Mossebärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
